--- a/data_extactor/batch_10_fa/trimmed/batch_0035_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0035_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | تاریخ و باستان‌شناسی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | هنرآموزان دوره دوم متوسطه | استادان علوم تربیتی و آموزش در آموزش عالی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره دوم متوسطه</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران آموزش استثنایی دوره دوم متوسطه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | مدیریت و امور اداری | ریاضیات</t>
+          <t>آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>هنرآموزان و معلمان فنی‌وحرفه‌ای دوره اول متوسطه | استادان و مربیان آموزش فنی‌وحرفه‌ای در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | کارشناسان برنامه‌ریزی و تدوین متون درسی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | ایمنی و امنیت عمومی | روان‌درمانی و مشاوره‌ | امور اداری و دفتری | خدمات مشتریان و خدمات فردی</t>
+          <t>آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی | درمان و مشاوره | اداری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و آمادگی | کمک‌آموزگاران مدارس استثنایی</t>
+          <t>متخصصان تربیت بدنی انطباقی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | روان‌شناسان مدارس | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | روان‌درمانی و مشاوره‌ | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | ریاضیات</t>
+          <t>آموزش و پرورش | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفت‌وگوی حضوری با همکاران و اولیا | ارتباط نزدیک و مستقیم با دانش‌آموزان | محیط سرپوشیده با تهویهٔ مطبوع | تعیین وظایف، اولویت‌ها و اهداف آموزشی | کار گروهی و تیمی | ایستادن طولانی‌مدت در محیط کلاس | آزادی عمل در تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | سخنرانی عمومی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مدیران مراکز پیش‌دبستانی و مهدکودک | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | معلمان آموزش استثنایی دوره ابتدایی | مربیان آموزش استثنایی پیش‌دبستانی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | روان‌شناسان مدارس | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | روان‌شناسی | روان‌درمانی و مشاوره‌</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | روان‌شناسی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مدیران مدارس ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | معلمان آموزش استثنایی دوره اول متوسطه | کمک‌آموزگاران مدارس استثنایی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | روان‌شناسان مدارس | معلمان آموزش استثنایی دوره اول متوسطه | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | ریاضیات | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>آموزش و پرورش | ریاضیات | اداری | خدمات مشتری و شخصی | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | روان‌شناسان مدرسه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌آموزگاران مدارس استثنایی</t>
+          <t>متخصصان تربیت بدنی انطباقی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | روان‌شناسان مدارس | معلمان آموزش استثنایی دوره ابتدایی | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نظارت | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | خدمات مشتریان و خدمات فردی | روان‌درمانی و مشاوره‌ | ریاضیات | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>آموزش و پرورش | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | ریاضیات | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان تربیت بدنی انطباقی | مدیران مدارس ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | کمک‌آموزگاران مدارس استثنایی</t>
+          <t>متخصصان تربیت بدنی انطباقی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و هدایت استعدادها | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | روان‌درمانی و مشاوره‌ | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | حقوق و مقررات دولتی</t>
+          <t>آموزش و پرورش | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفت‌وگوی حضوری با همکاران و ذی‌نفعان | سخنرانی در جمع و تدریس | کار گروهی و تیمی | محیط سرپوشیده با تهویهٔ مطبوع | تعیین وظایف، اولویت‌ها و اهداف کاری | آزادی عمل در تصمیم‌گیری | مواجهه با رفتارهای پرخاشگرانه و موقعیت‌های بحرانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره دوم متوسطه | کمک‌آموزگاران مدارس استثنایی | گفتاردرمانگران | مشاوران توانبخشی</t>
+          <t>معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان آموزش استثنایی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
+          <t>یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | زبان انگلیسی | روان‌درمانی و مشاوره‌ | خدمات مشتریان و خدمات فردی</t>
+          <t>آموزش و پرورش | روان‌شناسی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | هماهنگی عمومی بدن</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان علوم ورزشی و اوقات فراغت در آموزش عالی | کاردرمانگران تفریحی و حرکتی | روان‌شناسان مدرسه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | کمک‌آموزگاران مدارس استثنایی</t>
+          <t>معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | کارشناسان تفریح‌درمانی | روان‌شناسان مدارس | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره اول متوسطه | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | درک مطلب | شنیدن فعال | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>سخن گفتن | راهبردهای یادگیری | درک مطلب | گوش دادن فعال | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>استادان علوم تربیتی و آموزش در آموزش عالی | مشاوران تحصیلی، شغلی و راهنمایان آموزشی | آموزگاران دوره ابتدایی، به‌جز آموزش استثنایی | استادان زبان و ادبیات انگلیسی در آموزش عالی | کارشناسان برنامه‌ریزی و تدوین متون درسی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی شخصی</t>
+          <t>مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
